--- a/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
@@ -463,13 +463,13 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="6.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="1.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="1.853482" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="2.996339" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="3.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">

--- a/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
@@ -462,7 +462,7 @@
   <x:dimension ref="A1:H11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="6.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.710625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
